--- a/equipe/Marcio_Costa.xlsx
+++ b/equipe/Marcio_Costa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SuporteLead\Desktop\dashboard_analytics\equipe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89720A35-4EAD-45C1-A52C-725E6AE83C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA0427C-E325-4A7E-AF99-2CB1F7F4C233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{28FD2BDB-A87A-4B85-B83E-1AF1E0432417}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t xml:space="preserve">Quarter </t>
   </si>
@@ -835,19 +835,45 @@
       <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="11"/>
+      <c r="C4" s="5">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6">
+        <v>106</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="6">
+        <v>11</v>
+      </c>
+      <c r="H4" s="6">
+        <v>106</v>
+      </c>
+      <c r="I4" s="8">
+        <v>9.64</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10">
+        <v>0</v>
+      </c>
+      <c r="O4" s="11">
+        <v>0</v>
+      </c>
       <c r="P4" s="5"/>
       <c r="R4" t="s">
         <v>35</v>
